--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -30,13 +30,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/affiliation</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/affiliation</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-25T13:18:28+00:00</t>
+    <t>2026-10-29T07:06:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -341,7 +341,7 @@
     <t>checked-in-participant</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/checked-in-participant</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/checked-in-participant</t>
   </si>
   <si>
     <t>CheckedInParticipant</t>
@@ -508,7 +508,7 @@
     <t>Practitioner.extension:affiliation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/affiliation}
+    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/affiliation}
 </t>
   </si>
   <si>
@@ -518,7 +518,7 @@
     <t>primaryTrack</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/primary-track}
+    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/primary-track}
 </t>
   </si>
   <si>
@@ -674,7 +674,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/identifier/participant-2026</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/identifier/participant-2026</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1248,7 +1248,7 @@
     <t>Practitioner.qualification:eventRole.code</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/ValueSet/participation-roles</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/ValueSet/participation-roles</t>
   </si>
   <si>
     <t>Practitioner.qualification:eventRole.code.id</t>
@@ -1318,7 +1318,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/CodeSystem/participation-role</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/CodeSystem/participation-role</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1444,7 +1444,7 @@
     <t>checkin-list</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/checkin-list</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/checkin-list</t>
   </si>
   <si>
     <t>CheckinList</t>
@@ -1459,7 +1459,7 @@
     <t>List</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/event-list</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/event-list</t>
   </si>
   <si>
     <t>Collection
@@ -1589,13 +1589,13 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://hl7.no/fhir/ig/hackathon-attendance-registration-app/CodeSystem/list-purpose"/&gt;
+    &lt;system value="https://hl7.no/fhir/ig/hackathon-check-in-app/CodeSystem/list-purpose"/&gt;
     &lt;code value="checkins"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/ValueSet/list-purposes</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/ValueSet/list-purposes</t>
   </si>
   <si>
     <t>List.subject</t>
@@ -1734,7 +1734,7 @@
     <t>manualRegistration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/manual-registration}
+    <t xml:space="preserve">Extension {https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/manual-registration}
 </t>
   </si>
   <si>
@@ -1805,7 +1805,7 @@
     <t>List.entry.item</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/checked-in-participant)
+    <t xml:space="preserve">Reference(https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/checked-in-participant)
 </t>
   </si>
   <si>
@@ -1938,7 +1938,7 @@
     <t>expected-participant</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/expected-participant</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/expected-participant</t>
   </si>
   <si>
     <t>ExpectedParticipant</t>
@@ -2277,7 +2277,7 @@
     <t>manual-registration</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/manual-registration</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/manual-registration</t>
   </si>
   <si>
     <t>ManualRegistration</t>
@@ -2289,19 +2289,19 @@
     <t>primary-track</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/primary-track</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/primary-track</t>
   </si>
   <si>
     <t>PrimaryTrack</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/ValueSet/tracks</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/ValueSet/tracks</t>
   </si>
   <si>
     <t>roster-list</t>
   </si>
   <si>
-    <t>https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/roster-list</t>
+    <t>https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/roster-list</t>
   </si>
   <si>
     <t>RosterList</t>
@@ -2313,7 +2313,7 @@
     <t>Lists attendees and organizers registered for the event, with each person's participation role.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.no/fhir/ig/hackathon-attendance-registration-app/StructureDefinition/expected-participant)
+    <t xml:space="preserve">Reference(https://hl7.no/fhir/ig/hackathon-check-in-app/StructureDefinition/expected-participant)
 </t>
   </si>
 </sst>
@@ -3812,14 +3812,14 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="86.65625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="74.640625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="87.8671875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="70.4609375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="58.4453125" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="22.4453125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:06:30+00:00</t>
+    <t>2026-10-29T08:26:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:26:45+00:00</t>
+    <t>2026-10-29T09:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:23:29+00:00</t>
+    <t>2026-10-29T13:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:05:39+00:00</t>
+    <t>2026-10-29T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T15:50:41+00:00</t>
+    <t>2026-10-29T16:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T16:44:10+00:00</t>
+    <t>2026-10-30T09:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
